--- a/data/trans_dic/IP31KM02_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM02_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>63,98%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36,97; 72,08</t>
+          <t>56,2; 78,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>52,17; 74,58</t>
+          <t>48,13; 71,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49,11; 70,48</t>
+          <t>55,37; 72,48</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>58,6%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>44,37; 59,77</t>
+          <t>53,0; 62,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,18; 61,53</t>
+          <t>54,69; 62,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49,88; 59,11</t>
+          <t>55,36; 61,92</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>61,27%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>52,92; 65,79</t>
+          <t>55,28; 67,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53,39; 67,39</t>
+          <t>53,68; 66,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55,8; 65,0</t>
+          <t>56,56; 66,24</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>59,65%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>48,79; 60,41</t>
+          <t>56,0; 63,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>54,2; 61,97</t>
+          <t>56,12; 62,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53,34; 59,73</t>
+          <t>57,06; 62,14</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>40</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>30755</t>
+          <t>36028</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37810</t>
+          <t>27713</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68565</t>
+          <t>63741</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19855; 38708</t>
+          <t>30188; 41968</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>30439; 43515</t>
+          <t>22092; 32868</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55029; 78969</t>
+          <t>55160; 72202</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>367</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>246613</t>
+          <t>271742</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>285657</t>
+          <t>250404</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>532269</t>
+          <t>522147</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>200474; 270069</t>
+          <t>247216; 291988</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>258594; 310875</t>
+          <t>232232; 264762</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>477428; 565741</t>
+          <t>493327; 551751</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>136</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>87536</t>
+          <t>103064</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>110153</t>
+          <t>89205</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>197689</t>
+          <t>192269</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>77361; 96179</t>
+          <t>92141; 112916</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>96709; 122063</t>
+          <t>78986; 98538</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>182634; 212772</t>
+          <t>177489; 207890</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>543</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>568</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>364904</t>
+          <t>410834</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>433620</t>
+          <t>367322</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>798524</t>
+          <t>778156</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>317995; 393730</t>
+          <t>384652; 434676</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>403613; 461505</t>
+          <t>346671; 386522</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>744857; 834060</t>
+          <t>744314; 810592</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM02_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM02_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que toman una 2ª pieza de fruta todos los días (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>67,07%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>60,37%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>63,98%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>56,2; 78,13</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>48,13; 71,6</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>55,37; 72,48</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>58,26%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>58,96%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>58,6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>53,0; 62,6</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>54,69; 62,35</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>55,36; 61,92</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>61,83%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>60,63%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>61,27%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>55,28; 67,74</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>53,68; 66,97</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>56,56; 66,24</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>59,82%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>59,47%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>59,65%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>56,0; 63,29</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>56,12; 62,57</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>57,06; 62,14</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.6707197875741326</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.603704321916162</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.6398389846859371</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>36028</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>27713</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>63741</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.5619998910493852</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.4812601451902638</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.5537055486182194</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>30188; 41968</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>22092; 32868</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>55160; 72202</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.7813030606709049</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.7160006243018741</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.7247745225630287</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>367</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>739</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.5826089651345973</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.5896495748074246</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.5859643066097608</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>271742</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>250404</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>522147</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.5300258430468155</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.5468577199524834</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.5536224895489837</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>247216; 291988</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>232232; 264762</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>493327; 551751</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.6260146855779645</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.6234593375134354</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.6191864503767572</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.6183135328110226</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.606260219731405</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.612662232408288</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>103064</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>89205</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>192269</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.5527799996922416</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.5368073938357742</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.5655669884584296</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>92141; 112916</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>78986; 98538</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>177489; 207890</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.6774166366488475</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.6696879676676475</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.6624407073400541</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>568</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>543</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1111</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.5981650478493215</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.5946507261285013</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.596500979369288</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>410834</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>367322</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>778156</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.5600451767137267</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.5612183854294438</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.5705585274833769</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>384652; 434676</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>346671; 386522</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>744314; 810592</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.6328778798302169</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.6257335500373488</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.6213646170027797</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que toman una 2ª pieza de fruta todos los días (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>36028</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>27713</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>63741</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>30188</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>22092</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>55160</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>41968</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>32868</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>72202</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>372</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>367</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>271742</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>250404</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>522147</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>247216</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>232232</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>493327</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>291988</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>264762</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>551751</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>146</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>136</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>103064</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>89205</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>192269</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>92141</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>78986</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>177489</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>112916</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>98538</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>207890</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>568</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>543</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>410834</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>367322</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>778156</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>384652</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>346671</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>744314</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>434676</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>386522</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>810592</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>